--- a/data/trans_bre/IP16A04-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A04-Estudios-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 0,0</t>
+          <t>-15,67; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,56</t>
+          <t>0,0; 12,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 2,53</t>
+          <t>-1,6; 2,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,0</t>
+          <t>-2,33; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 5,04</t>
+          <t>-1,51; 5,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-92,73; —</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 13,29</t>
+          <t>-4,62; 11,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 0,0</t>
+          <t>-9,93; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 2,22</t>
+          <t>-2,79; 1,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,37</t>
+          <t>-1,98; 0,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 4,01</t>
+          <t>-0,62; 3,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,73; —</t>
+          <t>-73,36; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A04-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A04-Estudios-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 0,0</t>
+          <t>-17,23; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,52</t>
+          <t>0,0; 12,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,5</t>
+          <t>-1,62; 2,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,0</t>
+          <t>-2,11; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 5,2</t>
+          <t>-1,55; 5,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-92,73; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 11,44</t>
+          <t>-4,61; 12,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 0,0</t>
+          <t>-8,77; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,69</t>
+          <t>0,0; 12,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 1,91</t>
+          <t>-2,64; 1,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,37</t>
+          <t>-2,3; 0,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,9</t>
+          <t>-0,69; 4,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,36; —</t>
+          <t>-76,63; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A04-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A04-Estudios-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos laxantes</t>
+          <t>Menores que consumieron medicamentos laxantes</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,23; 0,0</t>
+          <t>-17,41; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,77</t>
+          <t>0,0; 13,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,51</t>
+          <t>-1,61; 2,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,0</t>
+          <t>-2,48; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 5,12</t>
+          <t>-1,35; 5,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 12,28</t>
+          <t>-4,58; 13,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 0,0</t>
+          <t>-9,96; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,24</t>
+          <t>0,0; 9,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 1,89</t>
+          <t>-2,56; 2,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,36</t>
+          <t>-1,97; 0,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 4,05</t>
+          <t>-0,49; 4,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-76,63; —</t>
+          <t>-79,73; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A04-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A04-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,135 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-3,32</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,46</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>-0.7749847697808043</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.6825533785089016</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-17,41; 0,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 13,56</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.882387913211945</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.540746201489215</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>122,27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,61; 2,53</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,48; 0,0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,35; 5,04</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.01452846891007633</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.122764010363802</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.4185803167533038</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.0992750381294569</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1.493592834176205</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,09</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,8</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,93</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>47,48%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.2934290830145977</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.7371549649913745</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.2121398080014099</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-4,58; 13,29</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-9,96; 0,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,69</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.4988488458738627</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.266812893369858</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,34 +739,24 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,38</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,64</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,55</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-24,86%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-65,71%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>168,01%</t>
+      <c r="C10" s="5" t="n">
+        <v>-0.0736580854399079</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.7415612109534261</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.4212073598617134</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-0.1432666467064616</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -869,42 +764,116 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,56; 2,22</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,97; 0,37</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,49; 4,01</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-79,73; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.036213131106948</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.254551510119241</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.8868549550444589</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.176277878277101</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.09164797542801457</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.1612655929852077</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.3879613443850362</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.3029466352130039</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.6463841375721124</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>2.109763701416357</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.5255364464783018</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.4985431887769688</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.107494023971011</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-0.8703936151553124</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.3269056585338249</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.1766851064464945</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9285651670907691</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -913,12 +882,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
